--- a/05_manual_check/manual_annotation_template.xlsx
+++ b/05_manual_check/manual_annotation_template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,45 +446,65 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>previous_sentence</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>next_sentence</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>trigger_terms</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>trigger_categories</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>keyword_score</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>auto_matched_pathway</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>matched_keywords</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>manual_pathway</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ethanol_specific</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
